--- a/src/test/java/com/nablarch/example/app/batch/ProjectCreationServiceActionTest.xlsx
+++ b/src/test/java/com/nablarch/example/app/batch/ProjectCreationServiceActionTest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tikK88843\git\nablarch-example-db-queue\src\test\java\com\nablarch\example\app\batch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\ClaudeCode\home\k10949\workspace\nablarch-example-db-queue\src\test\java\com\nablarch\example\app\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09152A4-D4F3-46D1-ADD6-4A4410593386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AF2AD1-82B6-4F42-BF27-8AD87F60D6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="489" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33225" yWindow="1545" windowWidth="21600" windowHeight="11235" tabRatio="489" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="setUpDb" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="143">
   <si>
     <t>no</t>
   </si>
@@ -880,6 +880,10 @@
   </si>
   <si>
     <t>0000000004</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXPECTED_TABLE[4]=PROJECT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1076,63 +1080,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1153,9 +1150,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1193,9 +1190,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1228,26 +1225,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1280,26 +1260,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1474,9 +1437,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1"/>
@@ -1488,43 +1451,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R94"/>
-  <sheetFormatPr defaultRowHeight="10.5"/>
+  <dimension ref="A1:Q94"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="10.199999999999999"/>
   <cols>
-    <col min="1" max="1" width="57.85546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="65" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="113" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="38.28515625" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="34.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="1" width="57.875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="65" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="113" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="38.25" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.375" style="19" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="34.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="29.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:17" ht="29.4">
+      <c r="A1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-    </row>
-    <row r="2" spans="1:18" s="21" customFormat="1">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+    </row>
+    <row r="2" spans="1:17" s="20" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -1536,7 +1499,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:18" s="21" customFormat="1">
+    <row r="3" spans="1:17" s="20" customFormat="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +1525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="4" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1572,7 +1535,7 @@
       <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -1584,11 +1547,11 @@
       <c r="G4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="5" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
@@ -1598,7 +1561,7 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -1610,11 +1573,11 @@
       <c r="G5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="6" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A6" s="8" t="s">
         <v>85</v>
       </c>
@@ -1624,7 +1587,7 @@
       <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -1636,11 +1599,11 @@
       <c r="G6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="7" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A7" s="8" t="s">
         <v>96</v>
       </c>
@@ -1650,7 +1613,7 @@
       <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -1662,2130 +1625,2078 @@
       <c r="G7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="29.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:17" ht="29.4">
+      <c r="A9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="15" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="15" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="14" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="22" t="s">
+      <c r="L12" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="22" t="s">
+      <c r="M12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N12" s="22" t="s">
+      <c r="N12" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="22" t="s">
+      <c r="O12" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P12" s="22" t="s">
+      <c r="P12" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="22" t="s">
+      <c r="Q12" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:17">
+      <c r="A13" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="23" t="s">
+      <c r="L13" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="N13" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O13" s="23" t="s">
+      <c r="O13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P13" s="23" t="s">
+      <c r="P13" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="Q13" s="23" t="s">
+      <c r="Q13" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="15" t="s">
+    <row r="14" spans="1:17">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="22" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L16" s="22" t="s">
+      <c r="L16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M16" s="22" t="s">
+      <c r="M16" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N16" s="22" t="s">
+      <c r="N16" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-    </row>
-    <row r="19" spans="1:16" s="25" customFormat="1" ht="29.25">
-      <c r="A19" s="28" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+    </row>
+    <row r="19" spans="1:16" ht="29.4">
+      <c r="A19" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="12"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="22" t="s">
+      <c r="I22" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K22" s="22" t="s">
+      <c r="K22" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="L22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M22" s="22" t="s">
+      <c r="M22" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N22" s="22" t="s">
+      <c r="N22" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O22" s="22" t="s">
+      <c r="O22" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P22" s="22" t="s">
+      <c r="P22" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H23" s="23" t="s">
+      <c r="H23" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="23" t="s">
+      <c r="I23" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K23" s="27" t="s">
+      <c r="K23" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L23" s="23" t="s">
+      <c r="L23" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="M23" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N23" s="23" t="s">
+      <c r="N23" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O23" s="23" t="s">
+      <c r="O23" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P23" s="23" t="s">
+      <c r="P23" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="22" t="s">
+      <c r="I26" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J26" s="22" t="s">
+      <c r="J26" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K26" s="22" t="s">
+      <c r="K26" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L26" s="22" t="s">
+      <c r="L26" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M26" s="22" t="s">
+      <c r="M26" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N26" s="22" t="s">
+      <c r="N26" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="23" t="s">
+      <c r="I27" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="27" t="s">
+      <c r="J27" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="K27" s="23" t="s">
+      <c r="K27" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="23" t="s">
+      <c r="L27" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="M27" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="N27" s="23" t="s">
+      <c r="N27" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="29.25">
-      <c r="A30" s="18" t="s">
+    <row r="30" spans="1:16" ht="29.4">
+      <c r="A30" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="12"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-    </row>
-    <row r="33" spans="1:18">
-      <c r="A33" s="14" t="s">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I33" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J33" s="22" t="s">
+      <c r="J33" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K33" s="22" t="s">
+      <c r="K33" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L33" s="22" t="s">
+      <c r="L33" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M33" s="22" t="s">
+      <c r="M33" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N33" s="22" t="s">
+      <c r="N33" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O33" s="22" t="s">
+      <c r="O33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P33" s="22" t="s">
+      <c r="P33" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q33" s="22" t="s">
+      <c r="Q33" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
-      <c r="A34" s="13" t="s">
+    <row r="34" spans="1:17">
+      <c r="A34" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23" t="s">
+      <c r="F34" s="22"/>
+      <c r="G34" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="J34" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K34" s="27" t="s">
+      <c r="K34" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L34" s="23" t="s">
+      <c r="L34" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M34" s="23" t="s">
+      <c r="M34" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N34" s="23" t="s">
+      <c r="N34" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O34" s="23" t="s">
+      <c r="O34" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P34" s="23" t="s">
+      <c r="P34" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q34" s="23" t="s">
+      <c r="Q34" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-    </row>
-    <row r="36" spans="1:18">
-      <c r="A36" s="15" t="s">
+    <row r="35" spans="1:17">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-    </row>
-    <row r="37" spans="1:18">
-      <c r="A37" s="22" t="s">
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H37" s="22" t="s">
+      <c r="H37" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="22" t="s">
+      <c r="I37" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J37" s="22" t="s">
+      <c r="J37" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="K37" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
-      <c r="A38" s="27" t="s">
+    <row r="38" spans="1:17">
+      <c r="A38" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="23"/>
-    </row>
-    <row r="40" spans="1:18" s="25" customFormat="1" ht="29.25">
-      <c r="A40" s="28" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+    </row>
+    <row r="40" spans="1:17" ht="29.4">
+      <c r="A40" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41" s="15" t="s">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="12"/>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42" s="15" t="s">
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="11"/>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43" s="14" t="s">
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E43" s="22" t="s">
+      <c r="E43" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="22" t="s">
+      <c r="H43" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="22" t="s">
+      <c r="I43" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="22" t="s">
+      <c r="J43" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K43" s="22" t="s">
+      <c r="K43" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L43" s="22" t="s">
+      <c r="L43" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M43" s="22" t="s">
+      <c r="M43" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N43" s="22" t="s">
+      <c r="N43" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O43" s="22" t="s">
+      <c r="O43" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P43" s="22" t="s">
+      <c r="P43" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
-      <c r="A44" s="13" t="s">
+    <row r="44" spans="1:17">
+      <c r="A44" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D44" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F44" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="G44" s="23" t="s">
+      <c r="G44" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H44" s="23" t="s">
+      <c r="H44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J44" s="23" t="s">
+      <c r="J44" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K44" s="27" t="s">
+      <c r="K44" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L44" s="23" t="s">
+      <c r="L44" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M44" s="23" t="s">
+      <c r="M44" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N44" s="23" t="s">
+      <c r="N44" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O44" s="23" t="s">
+      <c r="O44" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P44" s="23" t="s">
+      <c r="P44" s="22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:17">
+      <c r="A46" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-    </row>
-    <row r="47" spans="1:18">
-      <c r="A47" s="22" t="s">
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="22" t="s">
+      <c r="F47" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G47" s="22" t="s">
+      <c r="G47" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="22" t="s">
+      <c r="H47" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I47" s="22" t="s">
+      <c r="I47" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J47" s="22" t="s">
+      <c r="J47" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K47" s="22" t="s">
+      <c r="K47" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L47" s="22" t="s">
+      <c r="L47" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="22" t="s">
+      <c r="M47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N47" s="22" t="s">
+      <c r="N47" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
-      <c r="A48" s="27" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E48" s="23" t="s">
+      <c r="E48" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="F48" s="23" t="s">
+      <c r="F48" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="G48" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H48" s="23" t="s">
+      <c r="H48" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I48" s="23" t="s">
+      <c r="I48" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="J48" s="27" t="s">
+      <c r="J48" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="K48" s="23" t="s">
+      <c r="K48" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="L48" s="23" t="s">
+      <c r="L48" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="M48" s="23" t="s">
+      <c r="M48" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="N48" s="23" t="s">
+      <c r="N48" s="22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="29.25">
-      <c r="A50" s="18" t="s">
+    <row r="50" spans="1:17" ht="29.4">
+      <c r="A50" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-    </row>
-    <row r="51" spans="1:18">
-      <c r="A51" s="15" t="s">
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="12"/>
-    </row>
-    <row r="52" spans="1:18">
-      <c r="A52" s="15" t="s">
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="11"/>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-    </row>
-    <row r="53" spans="1:18">
-      <c r="A53" s="14" t="s">
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="22" t="s">
+      <c r="E53" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="22" t="s">
+      <c r="F53" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G53" s="22" t="s">
+      <c r="G53" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H53" s="22" t="s">
+      <c r="H53" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I53" s="22" t="s">
+      <c r="I53" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J53" s="22" t="s">
+      <c r="J53" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K53" s="22" t="s">
+      <c r="K53" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L53" s="22" t="s">
+      <c r="L53" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M53" s="22" t="s">
+      <c r="M53" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N53" s="22" t="s">
+      <c r="N53" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O53" s="22" t="s">
+      <c r="O53" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P53" s="22" t="s">
+      <c r="P53" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q53" s="22" t="s">
+      <c r="Q53" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
-      <c r="A54" s="13" t="s">
+    <row r="54" spans="1:17">
+      <c r="A54" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D54" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E54" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F54" s="13" t="s">
+      <c r="F54" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G54" s="23" t="s">
+      <c r="G54" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H54" s="23" t="s">
+      <c r="H54" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I54" s="23" t="s">
+      <c r="I54" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J54" s="23" t="s">
+      <c r="J54" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K54" s="27" t="s">
+      <c r="K54" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L54" s="23" t="s">
+      <c r="L54" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M54" s="23" t="s">
+      <c r="M54" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N54" s="23" t="s">
+      <c r="N54" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O54" s="23" t="s">
+      <c r="O54" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P54" s="23" t="s">
+      <c r="P54" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q54" s="23" t="s">
+      <c r="Q54" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="25"/>
-      <c r="N55" s="25"/>
-      <c r="O55" s="25"/>
-      <c r="P55" s="25"/>
-      <c r="Q55" s="25"/>
-      <c r="R55" s="25"/>
-    </row>
-    <row r="56" spans="1:18">
-      <c r="A56" s="15" t="s">
+    <row r="55" spans="1:17">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-    </row>
-    <row r="57" spans="1:18">
-      <c r="A57" s="22" t="s">
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F57" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H57" s="22" t="s">
+      <c r="H57" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I57" s="22" t="s">
+      <c r="I57" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J57" s="22" t="s">
+      <c r="J57" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K57" s="22" t="s">
+      <c r="K57" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L57" s="22" t="s">
+      <c r="L57" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M57" s="22" t="s">
+      <c r="M57" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N57" s="22" t="s">
+      <c r="N57" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
-      <c r="A58" s="27" t="s">
+    <row r="58" spans="1:17">
+      <c r="A58" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="23"/>
-    </row>
-    <row r="60" spans="1:18" s="25" customFormat="1" ht="29.25">
-      <c r="A60" s="28" t="s">
+      <c r="B58" s="15"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+    </row>
+    <row r="60" spans="1:17" ht="29.4">
+      <c r="A60" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-    </row>
-    <row r="61" spans="1:18">
-      <c r="A61" s="15" t="s">
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="12"/>
-    </row>
-    <row r="62" spans="1:18">
-      <c r="A62" s="15" t="s">
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="11"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-    </row>
-    <row r="63" spans="1:18">
-      <c r="A63" s="14" t="s">
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="A63" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F63" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G63" s="22" t="s">
+      <c r="G63" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I63" s="22" t="s">
+      <c r="I63" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J63" s="22" t="s">
+      <c r="J63" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K63" s="22" t="s">
+      <c r="K63" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L63" s="22" t="s">
+      <c r="L63" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M63" s="22" t="s">
+      <c r="M63" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N63" s="22" t="s">
+      <c r="N63" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O63" s="22" t="s">
+      <c r="O63" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P63" s="22" t="s">
+      <c r="P63" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
-      <c r="A64" s="13" t="s">
+    <row r="64" spans="1:17">
+      <c r="A64" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D64" s="24" t="s">
+      <c r="D64" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E64" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H64" s="23" t="s">
+      <c r="H64" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I64" s="23" t="s">
+      <c r="I64" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J64" s="23" t="s">
+      <c r="J64" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K64" s="27" t="s">
+      <c r="K64" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L64" s="23" t="s">
+      <c r="L64" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M64" s="23" t="s">
+      <c r="M64" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N64" s="23" t="s">
+      <c r="N64" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O64" s="23" t="s">
+      <c r="O64" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P64" s="23" t="s">
+      <c r="P64" s="22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
-      <c r="A66" s="15" t="s">
+    <row r="66" spans="1:17">
+      <c r="A66" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-    </row>
-    <row r="67" spans="1:18">
-      <c r="A67" s="22" t="s">
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+    </row>
+    <row r="67" spans="1:17">
+      <c r="A67" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C67" s="22" t="s">
+      <c r="C67" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D67" s="22" t="s">
+      <c r="D67" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F67" s="22" t="s">
+      <c r="F67" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G67" s="22" t="s">
+      <c r="G67" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="22" t="s">
+      <c r="H67" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I67" s="22" t="s">
+      <c r="I67" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J67" s="22" t="s">
+      <c r="J67" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K67" s="22" t="s">
+      <c r="K67" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L67" s="22" t="s">
+      <c r="L67" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M67" s="22" t="s">
+      <c r="M67" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N67" s="22" t="s">
+      <c r="N67" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
-      <c r="A68" s="27" t="s">
+    <row r="68" spans="1:17">
+      <c r="A68" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F68" s="23" t="s">
+      <c r="F68" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G68" s="23" t="s">
+      <c r="G68" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H68" s="23" t="s">
+      <c r="H68" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I68" s="23" t="s">
+      <c r="I68" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="J68" s="27" t="s">
+      <c r="J68" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="K68" s="23" t="s">
+      <c r="K68" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="L68" s="23" t="s">
+      <c r="L68" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="M68" s="23" t="s">
+      <c r="M68" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="N68" s="23" t="s">
+      <c r="N68" s="22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="29.25">
-      <c r="A70" s="18" t="s">
+    <row r="70" spans="1:17" ht="29.4">
+      <c r="A70" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="19"/>
-      <c r="L70" s="19"/>
-      <c r="M70" s="19"/>
-    </row>
-    <row r="71" spans="1:18">
-      <c r="A71" s="15" t="s">
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+    </row>
+    <row r="71" spans="1:17">
+      <c r="A71" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="12"/>
-    </row>
-    <row r="72" spans="1:18">
-      <c r="A72" s="15" t="s">
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="11"/>
+    </row>
+    <row r="72" spans="1:17">
+      <c r="A72" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15"/>
-    </row>
-    <row r="73" spans="1:18">
-      <c r="A73" s="14" t="s">
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F73" s="22" t="s">
+      <c r="F73" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G73" s="22" t="s">
+      <c r="G73" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H73" s="22" t="s">
+      <c r="H73" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I73" s="22" t="s">
+      <c r="I73" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J73" s="22" t="s">
+      <c r="J73" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K73" s="22" t="s">
+      <c r="K73" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L73" s="22" t="s">
+      <c r="L73" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M73" s="22" t="s">
+      <c r="M73" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N73" s="22" t="s">
+      <c r="N73" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O73" s="22" t="s">
+      <c r="O73" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P73" s="22" t="s">
+      <c r="P73" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q73" s="22" t="s">
+      <c r="Q73" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:18">
-      <c r="A74" s="13" t="s">
+    <row r="74" spans="1:17">
+      <c r="A74" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="D74" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E74" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F74" s="13" t="s">
+      <c r="F74" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G74" s="23" t="s">
+      <c r="G74" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H74" s="23" t="s">
+      <c r="H74" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="I74" s="23" t="s">
+      <c r="I74" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J74" s="23" t="s">
+      <c r="J74" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K74" s="27" t="s">
+      <c r="K74" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L74" s="23" t="s">
+      <c r="L74" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M74" s="23" t="s">
+      <c r="M74" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N74" s="23" t="s">
+      <c r="N74" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O74" s="23" t="s">
+      <c r="O74" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P74" s="23" t="s">
+      <c r="P74" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="Q74" s="23" t="s">
+      <c r="Q74" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
-      <c r="A75" s="13" t="s">
+    <row r="75" spans="1:17">
+      <c r="A75" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D75" s="24" t="s">
+      <c r="D75" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E75" s="13" t="s">
+      <c r="E75" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F75" s="13" t="s">
+      <c r="F75" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="G75" s="23" t="s">
+      <c r="G75" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H75" s="23" t="s">
+      <c r="H75" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I75" s="23" t="s">
+      <c r="I75" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J75" s="23" t="s">
+      <c r="J75" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="K75" s="27" t="s">
+      <c r="K75" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="L75" s="23" t="s">
+      <c r="L75" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="M75" s="23" t="s">
+      <c r="M75" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="N75" s="23" t="s">
+      <c r="N75" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="O75" s="23" t="s">
+      <c r="O75" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="P75" s="23" t="s">
+      <c r="P75" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q75" s="23" t="s">
+      <c r="Q75" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
-      <c r="A76" s="13" t="s">
+    <row r="76" spans="1:17">
+      <c r="A76" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D76" s="24" t="s">
+      <c r="D76" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F76" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G76" s="23" t="s">
+      <c r="G76" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="H76" s="23" t="s">
+      <c r="H76" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="I76" s="23" t="s">
+      <c r="I76" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="J76" s="23" t="s">
+      <c r="J76" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="K76" s="27" t="s">
+      <c r="K76" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="L76" s="23" t="s">
+      <c r="L76" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="M76" s="23" t="s">
+      <c r="M76" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="N76" s="23" t="s">
+      <c r="N76" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="O76" s="23" t="s">
+      <c r="O76" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="P76" s="23" t="s">
+      <c r="P76" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q76" s="23" t="s">
+      <c r="Q76" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
-      <c r="A77" s="13" t="s">
+    <row r="77" spans="1:17">
+      <c r="A77" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="13" t="s">
+      <c r="E77" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F77" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G77" s="23" t="s">
+      <c r="G77" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H77" s="23" t="s">
+      <c r="H77" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="I77" s="23" t="s">
+      <c r="I77" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="J77" s="23" t="s">
+      <c r="J77" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="K77" s="27" t="s">
+      <c r="K77" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="L77" s="23" t="s">
+      <c r="L77" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="M77" s="23" t="s">
+      <c r="M77" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="N77" s="23" t="s">
+      <c r="N77" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="O77" s="23" t="s">
+      <c r="O77" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="P77" s="23" t="s">
+      <c r="P77" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="Q77" s="23" t="s">
+      <c r="Q77" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="26"/>
-      <c r="M78" s="25"/>
-      <c r="N78" s="25"/>
-      <c r="O78" s="25"/>
-      <c r="P78" s="25"/>
-      <c r="Q78" s="25"/>
-      <c r="R78" s="25"/>
-    </row>
-    <row r="79" spans="1:18">
-      <c r="A79" s="15" t="s">
+    <row r="78" spans="1:17">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+    </row>
+    <row r="79" spans="1:17">
+      <c r="A79" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-    </row>
-    <row r="80" spans="1:18">
-      <c r="A80" s="22" t="s">
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+    </row>
+    <row r="80" spans="1:17">
+      <c r="A80" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B80" s="22" t="s">
+      <c r="B80" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C80" s="22" t="s">
+      <c r="C80" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D80" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F80" s="22" t="s">
+      <c r="F80" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G80" s="22" t="s">
+      <c r="G80" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H80" s="22" t="s">
+      <c r="H80" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I80" s="22" t="s">
+      <c r="I80" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J80" s="22" t="s">
+      <c r="J80" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K80" s="22" t="s">
+      <c r="K80" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L80" s="22" t="s">
+      <c r="L80" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M80" s="22" t="s">
+      <c r="M80" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N80" s="22" t="s">
+      <c r="N80" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:16">
-      <c r="A81" s="27" t="s">
+      <c r="A81" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B81" s="16"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="27"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-    </row>
-    <row r="83" spans="1:16" s="25" customFormat="1" ht="29.25">
-      <c r="A83" s="28" t="s">
+      <c r="B81" s="15"/>
+      <c r="C81" s="23"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="24"/>
+      <c r="K81" s="22"/>
+      <c r="L81" s="22"/>
+      <c r="M81" s="22"/>
+      <c r="N81" s="22"/>
+    </row>
+    <row r="83" spans="1:16" ht="29.4">
+      <c r="A83" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="29"/>
-      <c r="J83" s="29"/>
-      <c r="K83" s="29"/>
-      <c r="L83" s="29"/>
-      <c r="M83" s="29"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
+      <c r="L83" s="18"/>
+      <c r="M83" s="18"/>
     </row>
     <row r="84" spans="1:16">
-      <c r="A84" s="15" t="s">
+      <c r="A84" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="12"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="11"/>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
     </row>
     <row r="86" spans="1:16">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="B86" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="22" t="s">
+      <c r="C86" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D86" s="22" t="s">
+      <c r="D86" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="E86" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F86" s="22" t="s">
+      <c r="F86" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G86" s="22" t="s">
+      <c r="G86" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H86" s="22" t="s">
+      <c r="H86" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I86" s="22" t="s">
+      <c r="I86" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J86" s="22" t="s">
+      <c r="J86" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K86" s="22" t="s">
+      <c r="K86" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L86" s="22" t="s">
+      <c r="L86" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M86" s="22" t="s">
+      <c r="M86" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N86" s="22" t="s">
+      <c r="N86" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O86" s="22" t="s">
+      <c r="O86" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P86" s="22" t="s">
+      <c r="P86" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:16">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D87" s="24" t="s">
+      <c r="D87" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E87" s="13" t="s">
+      <c r="E87" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F87" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G87" s="23" t="s">
+      <c r="G87" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H87" s="23" t="s">
+      <c r="H87" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="I87" s="23" t="s">
+      <c r="I87" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J87" s="23" t="s">
+      <c r="J87" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K87" s="27" t="s">
+      <c r="K87" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L87" s="23" t="s">
+      <c r="L87" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M87" s="23" t="s">
+      <c r="M87" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N87" s="23" t="s">
+      <c r="N87" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O87" s="23" t="s">
+      <c r="O87" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P87" s="23" t="s">
+      <c r="P87" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:16">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="16" t="s">
+      <c r="C88" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D88" s="24" t="s">
+      <c r="D88" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E88" s="13" t="s">
+      <c r="E88" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F88" s="13" t="s">
+      <c r="F88" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G88" s="23" t="s">
+      <c r="G88" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H88" s="23" t="s">
+      <c r="H88" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I88" s="23" t="s">
+      <c r="I88" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J88" s="23" t="s">
+      <c r="J88" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="K88" s="27" t="s">
+      <c r="K88" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="L88" s="23" t="s">
+      <c r="L88" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="M88" s="23" t="s">
+      <c r="M88" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="N88" s="23" t="s">
+      <c r="N88" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="O88" s="23" t="s">
+      <c r="O88" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="P88" s="23" t="s">
+      <c r="P88" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:16">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D89" s="24" t="s">
+      <c r="D89" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E89" s="13" t="s">
+      <c r="E89" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F89" s="13" t="s">
+      <c r="F89" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G89" s="23" t="s">
+      <c r="G89" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="H89" s="23" t="s">
+      <c r="H89" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="I89" s="23" t="s">
+      <c r="I89" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="J89" s="23" t="s">
+      <c r="J89" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="K89" s="27" t="s">
+      <c r="K89" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="L89" s="23" t="s">
+      <c r="L89" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="M89" s="23" t="s">
+      <c r="M89" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="N89" s="23" t="s">
+      <c r="N89" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="O89" s="23" t="s">
+      <c r="O89" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="P89" s="23" t="s">
+      <c r="P89" s="22" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C90" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D90" s="24" t="s">
+      <c r="D90" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E90" s="13" t="s">
+      <c r="E90" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F90" s="13" t="s">
+      <c r="F90" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G90" s="23" t="s">
+      <c r="G90" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H90" s="23" t="s">
+      <c r="H90" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="I90" s="23" t="s">
+      <c r="I90" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="J90" s="23" t="s">
+      <c r="J90" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="K90" s="27" t="s">
+      <c r="K90" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="L90" s="23" t="s">
+      <c r="L90" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="M90" s="23" t="s">
+      <c r="M90" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="N90" s="23" t="s">
+      <c r="N90" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="O90" s="23" t="s">
+      <c r="O90" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="P90" s="23" t="s">
+      <c r="P90" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
+      <c r="A92" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="22" t="s">
+      <c r="C93" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D93" s="22" t="s">
+      <c r="D93" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E93" s="22" t="s">
+      <c r="E93" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F93" s="22" t="s">
+      <c r="F93" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G93" s="22" t="s">
+      <c r="G93" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H93" s="22" t="s">
+      <c r="H93" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I93" s="22" t="s">
+      <c r="I93" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J93" s="22" t="s">
+      <c r="J93" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K93" s="22" t="s">
+      <c r="K93" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L93" s="22" t="s">
+      <c r="L93" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M93" s="22" t="s">
+      <c r="M93" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N93" s="22" t="s">
+      <c r="N93" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="27" t="s">
+      <c r="A94" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B94" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="13" t="s">
+      <c r="E94" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F94" s="23" t="s">
+      <c r="F94" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G94" s="23" t="s">
+      <c r="G94" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H94" s="23" t="s">
+      <c r="H94" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I94" s="23" t="s">
+      <c r="I94" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="J94" s="27" t="s">
+      <c r="J94" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="K94" s="23" t="s">
+      <c r="K94" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="23" t="s">
+      <c r="L94" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="M94" s="23" t="s">
+      <c r="M94" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N94" s="23" t="s">
+      <c r="N94" s="22" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3799,43 +3710,43 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="10.5"/>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="10.199999999999999"/>
   <cols>
-    <col min="1" max="1" width="57.85546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="65" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="113" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="38.28515625" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="34.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="1" width="57.875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="65" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="113" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="38.25" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.375" style="19" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="34.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="29.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:17" ht="29.4">
+      <c r="A1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-    </row>
-    <row r="2" spans="1:18" s="21" customFormat="1">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+    </row>
+    <row r="2" spans="1:17" s="20" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -3847,7 +3758,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:18" s="21" customFormat="1">
+    <row r="3" spans="1:17" s="20" customFormat="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -3873,7 +3784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="4" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -3883,7 +3794,7 @@
       <c r="C4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -3895,437 +3806,424 @@
       <c r="G4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="29.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:17" ht="29.4">
+      <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="15" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="15" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="14" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="22" t="s">
+      <c r="J9" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="22" t="s">
+      <c r="K9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="22" t="s">
+      <c r="L9" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="22" t="s">
+      <c r="M9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="22" t="s">
+      <c r="N9" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="22" t="s">
+      <c r="O9" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="22" t="s">
+      <c r="P9" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="22" t="s">
+      <c r="Q9" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:17">
+      <c r="A10" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="27" t="s">
+      <c r="K10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N10" s="23" t="s">
+      <c r="N10" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O10" s="23" t="s">
+      <c r="O10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P10" s="23" t="s">
+      <c r="P10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="Q10" s="23" t="s">
+      <c r="Q10" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="15" t="s">
+    <row r="12" spans="1:17">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="22" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="22" t="s">
+      <c r="L14" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="22" t="s">
+      <c r="N14" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="27" t="s">
+    <row r="15" spans="1:17">
+      <c r="A15" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-    </row>
-    <row r="17" spans="1:16" s="25" customFormat="1" ht="29.25">
-      <c r="A17" s="28" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+    </row>
+    <row r="17" spans="1:16" ht="29.4">
+      <c r="A17" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="12"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="22" t="s">
+      <c r="I20" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="22" t="s">
+      <c r="J20" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K20" s="22" t="s">
+      <c r="K20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="22" t="s">
+      <c r="L20" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M20" s="22" t="s">
+      <c r="M20" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N20" s="22" t="s">
+      <c r="N20" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="22" t="s">
+      <c r="O20" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="22" t="s">
+      <c r="P20" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J21" s="23" t="s">
+      <c r="J21" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="27" t="s">
+      <c r="K21" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L21" s="23" t="s">
+      <c r="L21" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M21" s="23" t="s">
+      <c r="M21" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N21" s="23" t="s">
+      <c r="N21" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="23" t="s">
+      <c r="O21" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P21" s="23" t="s">
+      <c r="P21" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J24" s="22" t="s">
+      <c r="J24" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="K24" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L24" s="22" t="s">
+      <c r="L24" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M24" s="22" t="s">
+      <c r="M24" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N24" s="22" t="s">
+      <c r="N24" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/src/test/java/com/nablarch/example/app/batch/ProjectCreationServiceActionTest.xlsx
+++ b/src/test/java/com/nablarch/example/app/batch/ProjectCreationServiceActionTest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tikK88843\git\nablarch-example-db-queue\src\test\java\com\nablarch\example\app\batch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\ClaudeCode\home\k10949\workspace\nablarch-example-db-queue\src\test\java\com\nablarch\example\app\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09152A4-D4F3-46D1-ADD6-4A4410593386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CED089-3C32-40E7-9EA6-137FCF2736E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="489" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34530" yWindow="2850" windowWidth="21600" windowHeight="11235" tabRatio="489" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="setUpDb" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="143">
   <si>
     <t>no</t>
   </si>
@@ -880,6 +880,10 @@
   </si>
   <si>
     <t>0000000004</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXPECTED_TABLE[4]=PROJECT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1076,63 +1080,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1153,9 +1150,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1193,9 +1190,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1228,26 +1225,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1280,26 +1260,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1474,9 +1437,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1"/>
@@ -1488,43 +1451,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R94"/>
-  <sheetFormatPr defaultRowHeight="10.5"/>
+  <dimension ref="A1:Q94"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="10.199999999999999"/>
   <cols>
-    <col min="1" max="1" width="57.85546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="65" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="113" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="38.28515625" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="34.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="1" width="57.875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="65" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="113" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="38.25" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.375" style="19" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="34.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="29.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:17" ht="29.4">
+      <c r="A1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-    </row>
-    <row r="2" spans="1:18" s="21" customFormat="1">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+    </row>
+    <row r="2" spans="1:17" s="20" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -1536,7 +1499,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:18" s="21" customFormat="1">
+    <row r="3" spans="1:17" s="20" customFormat="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +1525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="4" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1572,7 +1535,7 @@
       <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -1584,11 +1547,11 @@
       <c r="G4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="5" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
@@ -1598,7 +1561,7 @@
       <c r="C5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="8" t="s">
@@ -1610,11 +1573,11 @@
       <c r="G5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="6" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A6" s="8" t="s">
         <v>85</v>
       </c>
@@ -1624,7 +1587,7 @@
       <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -1636,11 +1599,11 @@
       <c r="G6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="7" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A7" s="8" t="s">
         <v>96</v>
       </c>
@@ -1650,7 +1613,7 @@
       <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="8" t="s">
@@ -1662,2130 +1625,2078 @@
       <c r="G7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="29.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:17" ht="29.4">
+      <c r="A9" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="15" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="15" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="14" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="22" t="s">
+      <c r="L12" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="22" t="s">
+      <c r="M12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N12" s="22" t="s">
+      <c r="N12" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O12" s="22" t="s">
+      <c r="O12" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P12" s="22" t="s">
+      <c r="P12" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="22" t="s">
+      <c r="Q12" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:17">
+      <c r="A13" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L13" s="23" t="s">
+      <c r="L13" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="N13" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O13" s="23" t="s">
+      <c r="O13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P13" s="23" t="s">
+      <c r="P13" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="Q13" s="23" t="s">
+      <c r="Q13" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="15" t="s">
+    <row r="14" spans="1:17">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="22" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L16" s="22" t="s">
+      <c r="L16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M16" s="22" t="s">
+      <c r="M16" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N16" s="22" t="s">
+      <c r="N16" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-    </row>
-    <row r="19" spans="1:16" s="25" customFormat="1" ht="29.25">
-      <c r="A19" s="28" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+    </row>
+    <row r="19" spans="1:16" ht="29.4">
+      <c r="A19" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="12"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="22" t="s">
+      <c r="I22" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K22" s="22" t="s">
+      <c r="K22" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="L22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M22" s="22" t="s">
+      <c r="M22" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N22" s="22" t="s">
+      <c r="N22" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O22" s="22" t="s">
+      <c r="O22" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P22" s="22" t="s">
+      <c r="P22" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="H23" s="23" t="s">
+      <c r="H23" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="23" t="s">
+      <c r="I23" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K23" s="27" t="s">
+      <c r="K23" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L23" s="23" t="s">
+      <c r="L23" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="M23" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N23" s="23" t="s">
+      <c r="N23" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O23" s="23" t="s">
+      <c r="O23" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P23" s="23" t="s">
+      <c r="P23" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="22" t="s">
+      <c r="I26" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J26" s="22" t="s">
+      <c r="J26" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K26" s="22" t="s">
+      <c r="K26" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L26" s="22" t="s">
+      <c r="L26" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M26" s="22" t="s">
+      <c r="M26" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N26" s="22" t="s">
+      <c r="N26" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="23" t="s">
+      <c r="I27" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="27" t="s">
+      <c r="J27" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="K27" s="23" t="s">
+      <c r="K27" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="23" t="s">
+      <c r="L27" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="M27" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="N27" s="23" t="s">
+      <c r="N27" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="29.25">
-      <c r="A30" s="18" t="s">
+    <row r="30" spans="1:16" ht="29.4">
+      <c r="A30" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="12"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-    </row>
-    <row r="33" spans="1:18">
-      <c r="A33" s="14" t="s">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I33" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J33" s="22" t="s">
+      <c r="J33" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K33" s="22" t="s">
+      <c r="K33" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L33" s="22" t="s">
+      <c r="L33" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M33" s="22" t="s">
+      <c r="M33" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N33" s="22" t="s">
+      <c r="N33" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O33" s="22" t="s">
+      <c r="O33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P33" s="22" t="s">
+      <c r="P33" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q33" s="22" t="s">
+      <c r="Q33" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
-      <c r="A34" s="13" t="s">
+    <row r="34" spans="1:17">
+      <c r="A34" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23" t="s">
+      <c r="F34" s="22"/>
+      <c r="G34" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J34" s="23" t="s">
+      <c r="J34" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K34" s="27" t="s">
+      <c r="K34" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L34" s="23" t="s">
+      <c r="L34" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M34" s="23" t="s">
+      <c r="M34" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N34" s="23" t="s">
+      <c r="N34" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O34" s="23" t="s">
+      <c r="O34" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P34" s="23" t="s">
+      <c r="P34" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q34" s="23" t="s">
+      <c r="Q34" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-    </row>
-    <row r="36" spans="1:18">
-      <c r="A36" s="15" t="s">
+    <row r="35" spans="1:17">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-    </row>
-    <row r="37" spans="1:18">
-      <c r="A37" s="22" t="s">
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H37" s="22" t="s">
+      <c r="H37" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="22" t="s">
+      <c r="I37" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J37" s="22" t="s">
+      <c r="J37" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K37" s="22" t="s">
+      <c r="K37" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L37" s="22" t="s">
+      <c r="L37" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M37" s="22" t="s">
+      <c r="M37" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N37" s="22" t="s">
+      <c r="N37" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
-      <c r="A38" s="27" t="s">
+    <row r="38" spans="1:17">
+      <c r="A38" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="23"/>
-    </row>
-    <row r="40" spans="1:18" s="25" customFormat="1" ht="29.25">
-      <c r="A40" s="28" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+      <c r="N38" s="22"/>
+    </row>
+    <row r="40" spans="1:17" ht="29.4">
+      <c r="A40" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41" s="15" t="s">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="12"/>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42" s="15" t="s">
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="11"/>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43" s="14" t="s">
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E43" s="22" t="s">
+      <c r="E43" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="22" t="s">
+      <c r="H43" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="22" t="s">
+      <c r="I43" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="22" t="s">
+      <c r="J43" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K43" s="22" t="s">
+      <c r="K43" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L43" s="22" t="s">
+      <c r="L43" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M43" s="22" t="s">
+      <c r="M43" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N43" s="22" t="s">
+      <c r="N43" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O43" s="22" t="s">
+      <c r="O43" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P43" s="22" t="s">
+      <c r="P43" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
-      <c r="A44" s="13" t="s">
+    <row r="44" spans="1:17">
+      <c r="A44" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D44" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F44" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="G44" s="23" t="s">
+      <c r="G44" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H44" s="23" t="s">
+      <c r="H44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J44" s="23" t="s">
+      <c r="J44" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K44" s="27" t="s">
+      <c r="K44" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L44" s="23" t="s">
+      <c r="L44" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M44" s="23" t="s">
+      <c r="M44" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N44" s="23" t="s">
+      <c r="N44" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O44" s="23" t="s">
+      <c r="O44" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P44" s="23" t="s">
+      <c r="P44" s="22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:17">
+      <c r="A46" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-    </row>
-    <row r="47" spans="1:18">
-      <c r="A47" s="22" t="s">
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="22" t="s">
+      <c r="F47" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G47" s="22" t="s">
+      <c r="G47" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="22" t="s">
+      <c r="H47" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I47" s="22" t="s">
+      <c r="I47" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J47" s="22" t="s">
+      <c r="J47" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K47" s="22" t="s">
+      <c r="K47" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L47" s="22" t="s">
+      <c r="L47" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="22" t="s">
+      <c r="M47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N47" s="22" t="s">
+      <c r="N47" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
-      <c r="A48" s="27" t="s">
+    <row r="48" spans="1:17">
+      <c r="A48" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E48" s="23" t="s">
+      <c r="E48" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="F48" s="23" t="s">
+      <c r="F48" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="G48" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H48" s="23" t="s">
+      <c r="H48" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I48" s="23" t="s">
+      <c r="I48" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="J48" s="27" t="s">
+      <c r="J48" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="K48" s="23" t="s">
+      <c r="K48" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="L48" s="23" t="s">
+      <c r="L48" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="M48" s="23" t="s">
+      <c r="M48" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="N48" s="23" t="s">
+      <c r="N48" s="22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="29.25">
-      <c r="A50" s="18" t="s">
+    <row r="50" spans="1:17" ht="29.4">
+      <c r="A50" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-    </row>
-    <row r="51" spans="1:18">
-      <c r="A51" s="15" t="s">
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="12"/>
-    </row>
-    <row r="52" spans="1:18">
-      <c r="A52" s="15" t="s">
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="11"/>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-    </row>
-    <row r="53" spans="1:18">
-      <c r="A53" s="14" t="s">
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="22" t="s">
+      <c r="E53" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="22" t="s">
+      <c r="F53" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G53" s="22" t="s">
+      <c r="G53" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H53" s="22" t="s">
+      <c r="H53" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I53" s="22" t="s">
+      <c r="I53" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J53" s="22" t="s">
+      <c r="J53" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K53" s="22" t="s">
+      <c r="K53" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L53" s="22" t="s">
+      <c r="L53" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M53" s="22" t="s">
+      <c r="M53" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N53" s="22" t="s">
+      <c r="N53" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O53" s="22" t="s">
+      <c r="O53" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P53" s="22" t="s">
+      <c r="P53" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q53" s="22" t="s">
+      <c r="Q53" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
-      <c r="A54" s="13" t="s">
+    <row r="54" spans="1:17">
+      <c r="A54" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D54" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E54" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F54" s="13" t="s">
+      <c r="F54" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G54" s="23" t="s">
+      <c r="G54" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H54" s="23" t="s">
+      <c r="H54" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I54" s="23" t="s">
+      <c r="I54" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J54" s="23" t="s">
+      <c r="J54" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K54" s="27" t="s">
+      <c r="K54" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L54" s="23" t="s">
+      <c r="L54" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M54" s="23" t="s">
+      <c r="M54" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N54" s="23" t="s">
+      <c r="N54" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O54" s="23" t="s">
+      <c r="O54" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P54" s="23" t="s">
+      <c r="P54" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q54" s="23" t="s">
+      <c r="Q54" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="25"/>
-      <c r="N55" s="25"/>
-      <c r="O55" s="25"/>
-      <c r="P55" s="25"/>
-      <c r="Q55" s="25"/>
-      <c r="R55" s="25"/>
-    </row>
-    <row r="56" spans="1:18">
-      <c r="A56" s="15" t="s">
+    <row r="55" spans="1:17">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-    </row>
-    <row r="57" spans="1:18">
-      <c r="A57" s="22" t="s">
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="B57" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F57" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H57" s="22" t="s">
+      <c r="H57" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I57" s="22" t="s">
+      <c r="I57" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J57" s="22" t="s">
+      <c r="J57" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K57" s="22" t="s">
+      <c r="K57" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L57" s="22" t="s">
+      <c r="L57" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M57" s="22" t="s">
+      <c r="M57" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N57" s="22" t="s">
+      <c r="N57" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
-      <c r="A58" s="27" t="s">
+    <row r="58" spans="1:17">
+      <c r="A58" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="23"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="23"/>
-    </row>
-    <row r="60" spans="1:18" s="25" customFormat="1" ht="29.25">
-      <c r="A60" s="28" t="s">
+      <c r="B58" s="15"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+    </row>
+    <row r="60" spans="1:17" ht="29.4">
+      <c r="A60" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-    </row>
-    <row r="61" spans="1:18">
-      <c r="A61" s="15" t="s">
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="12"/>
-    </row>
-    <row r="62" spans="1:18">
-      <c r="A62" s="15" t="s">
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="11"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-    </row>
-    <row r="63" spans="1:18">
-      <c r="A63" s="14" t="s">
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="A63" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F63" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G63" s="22" t="s">
+      <c r="G63" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I63" s="22" t="s">
+      <c r="I63" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J63" s="22" t="s">
+      <c r="J63" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K63" s="22" t="s">
+      <c r="K63" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L63" s="22" t="s">
+      <c r="L63" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M63" s="22" t="s">
+      <c r="M63" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N63" s="22" t="s">
+      <c r="N63" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O63" s="22" t="s">
+      <c r="O63" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P63" s="22" t="s">
+      <c r="P63" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
-      <c r="A64" s="13" t="s">
+    <row r="64" spans="1:17">
+      <c r="A64" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D64" s="24" t="s">
+      <c r="D64" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E64" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H64" s="23" t="s">
+      <c r="H64" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I64" s="23" t="s">
+      <c r="I64" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J64" s="23" t="s">
+      <c r="J64" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K64" s="27" t="s">
+      <c r="K64" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L64" s="23" t="s">
+      <c r="L64" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M64" s="23" t="s">
+      <c r="M64" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N64" s="23" t="s">
+      <c r="N64" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O64" s="23" t="s">
+      <c r="O64" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P64" s="23" t="s">
+      <c r="P64" s="22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
-      <c r="A66" s="15" t="s">
+    <row r="66" spans="1:17">
+      <c r="A66" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-    </row>
-    <row r="67" spans="1:18">
-      <c r="A67" s="22" t="s">
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+    </row>
+    <row r="67" spans="1:17">
+      <c r="A67" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="B67" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C67" s="22" t="s">
+      <c r="C67" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D67" s="22" t="s">
+      <c r="D67" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F67" s="22" t="s">
+      <c r="F67" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G67" s="22" t="s">
+      <c r="G67" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H67" s="22" t="s">
+      <c r="H67" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I67" s="22" t="s">
+      <c r="I67" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J67" s="22" t="s">
+      <c r="J67" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K67" s="22" t="s">
+      <c r="K67" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L67" s="22" t="s">
+      <c r="L67" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M67" s="22" t="s">
+      <c r="M67" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N67" s="22" t="s">
+      <c r="N67" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
-      <c r="A68" s="27" t="s">
+    <row r="68" spans="1:17">
+      <c r="A68" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F68" s="23" t="s">
+      <c r="F68" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G68" s="23" t="s">
+      <c r="G68" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H68" s="23" t="s">
+      <c r="H68" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I68" s="23" t="s">
+      <c r="I68" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="J68" s="27" t="s">
+      <c r="J68" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="K68" s="23" t="s">
+      <c r="K68" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="L68" s="23" t="s">
+      <c r="L68" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="M68" s="23" t="s">
+      <c r="M68" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="N68" s="23" t="s">
+      <c r="N68" s="22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="29.25">
-      <c r="A70" s="18" t="s">
+    <row r="70" spans="1:17" ht="29.4">
+      <c r="A70" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="19"/>
-      <c r="L70" s="19"/>
-      <c r="M70" s="19"/>
-    </row>
-    <row r="71" spans="1:18">
-      <c r="A71" s="15" t="s">
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+    </row>
+    <row r="71" spans="1:17">
+      <c r="A71" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="12"/>
-    </row>
-    <row r="72" spans="1:18">
-      <c r="A72" s="15" t="s">
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="11"/>
+    </row>
+    <row r="72" spans="1:17">
+      <c r="A72" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15"/>
-    </row>
-    <row r="73" spans="1:18">
-      <c r="A73" s="14" t="s">
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F73" s="22" t="s">
+      <c r="F73" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G73" s="22" t="s">
+      <c r="G73" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H73" s="22" t="s">
+      <c r="H73" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I73" s="22" t="s">
+      <c r="I73" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J73" s="22" t="s">
+      <c r="J73" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K73" s="22" t="s">
+      <c r="K73" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L73" s="22" t="s">
+      <c r="L73" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M73" s="22" t="s">
+      <c r="M73" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N73" s="22" t="s">
+      <c r="N73" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O73" s="22" t="s">
+      <c r="O73" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P73" s="22" t="s">
+      <c r="P73" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q73" s="22" t="s">
+      <c r="Q73" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:18">
-      <c r="A74" s="13" t="s">
+    <row r="74" spans="1:17">
+      <c r="A74" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="D74" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E74" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F74" s="13" t="s">
+      <c r="F74" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G74" s="23" t="s">
+      <c r="G74" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H74" s="23" t="s">
+      <c r="H74" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="I74" s="23" t="s">
+      <c r="I74" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J74" s="23" t="s">
+      <c r="J74" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K74" s="27" t="s">
+      <c r="K74" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L74" s="23" t="s">
+      <c r="L74" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M74" s="23" t="s">
+      <c r="M74" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N74" s="23" t="s">
+      <c r="N74" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O74" s="23" t="s">
+      <c r="O74" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P74" s="23" t="s">
+      <c r="P74" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="Q74" s="23" t="s">
+      <c r="Q74" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
-      <c r="A75" s="13" t="s">
+    <row r="75" spans="1:17">
+      <c r="A75" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D75" s="24" t="s">
+      <c r="D75" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E75" s="13" t="s">
+      <c r="E75" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F75" s="13" t="s">
+      <c r="F75" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="G75" s="23" t="s">
+      <c r="G75" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H75" s="23" t="s">
+      <c r="H75" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I75" s="23" t="s">
+      <c r="I75" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J75" s="23" t="s">
+      <c r="J75" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="K75" s="27" t="s">
+      <c r="K75" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="L75" s="23" t="s">
+      <c r="L75" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="M75" s="23" t="s">
+      <c r="M75" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="N75" s="23" t="s">
+      <c r="N75" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="O75" s="23" t="s">
+      <c r="O75" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="P75" s="23" t="s">
+      <c r="P75" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q75" s="23" t="s">
+      <c r="Q75" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
-      <c r="A76" s="13" t="s">
+    <row r="76" spans="1:17">
+      <c r="A76" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D76" s="24" t="s">
+      <c r="D76" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F76" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G76" s="23" t="s">
+      <c r="G76" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="H76" s="23" t="s">
+      <c r="H76" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="I76" s="23" t="s">
+      <c r="I76" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="J76" s="23" t="s">
+      <c r="J76" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="K76" s="27" t="s">
+      <c r="K76" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="L76" s="23" t="s">
+      <c r="L76" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="M76" s="23" t="s">
+      <c r="M76" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="N76" s="23" t="s">
+      <c r="N76" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="O76" s="23" t="s">
+      <c r="O76" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="P76" s="23" t="s">
+      <c r="P76" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q76" s="23" t="s">
+      <c r="Q76" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
-      <c r="A77" s="13" t="s">
+    <row r="77" spans="1:17">
+      <c r="A77" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E77" s="13" t="s">
+      <c r="E77" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F77" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G77" s="23" t="s">
+      <c r="G77" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H77" s="23" t="s">
+      <c r="H77" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="I77" s="23" t="s">
+      <c r="I77" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="J77" s="23" t="s">
+      <c r="J77" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="K77" s="27" t="s">
+      <c r="K77" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="L77" s="23" t="s">
+      <c r="L77" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="M77" s="23" t="s">
+      <c r="M77" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="N77" s="23" t="s">
+      <c r="N77" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="O77" s="23" t="s">
+      <c r="O77" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="P77" s="23" t="s">
+      <c r="P77" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="Q77" s="23" t="s">
+      <c r="Q77" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="26"/>
-      <c r="M78" s="25"/>
-      <c r="N78" s="25"/>
-      <c r="O78" s="25"/>
-      <c r="P78" s="25"/>
-      <c r="Q78" s="25"/>
-      <c r="R78" s="25"/>
-    </row>
-    <row r="79" spans="1:18">
-      <c r="A79" s="15" t="s">
+    <row r="78" spans="1:17">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+    </row>
+    <row r="79" spans="1:17">
+      <c r="A79" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-    </row>
-    <row r="80" spans="1:18">
-      <c r="A80" s="22" t="s">
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+    </row>
+    <row r="80" spans="1:17">
+      <c r="A80" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B80" s="22" t="s">
+      <c r="B80" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C80" s="22" t="s">
+      <c r="C80" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D80" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F80" s="22" t="s">
+      <c r="F80" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G80" s="22" t="s">
+      <c r="G80" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H80" s="22" t="s">
+      <c r="H80" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I80" s="22" t="s">
+      <c r="I80" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J80" s="22" t="s">
+      <c r="J80" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K80" s="22" t="s">
+      <c r="K80" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L80" s="22" t="s">
+      <c r="L80" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M80" s="22" t="s">
+      <c r="M80" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N80" s="22" t="s">
+      <c r="N80" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:16">
-      <c r="A81" s="27" t="s">
+      <c r="A81" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B81" s="16"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="23"/>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="27"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="23"/>
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-    </row>
-    <row r="83" spans="1:16" s="25" customFormat="1" ht="29.25">
-      <c r="A83" s="28" t="s">
+      <c r="B81" s="15"/>
+      <c r="C81" s="23"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="24"/>
+      <c r="K81" s="22"/>
+      <c r="L81" s="22"/>
+      <c r="M81" s="22"/>
+      <c r="N81" s="22"/>
+    </row>
+    <row r="83" spans="1:16" ht="29.4">
+      <c r="A83" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="29"/>
-      <c r="J83" s="29"/>
-      <c r="K83" s="29"/>
-      <c r="L83" s="29"/>
-      <c r="M83" s="29"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
+      <c r="L83" s="18"/>
+      <c r="M83" s="18"/>
     </row>
     <row r="84" spans="1:16">
-      <c r="A84" s="15" t="s">
+      <c r="A84" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="12"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="11"/>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
     </row>
     <row r="86" spans="1:16">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="B86" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="22" t="s">
+      <c r="C86" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D86" s="22" t="s">
+      <c r="D86" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="E86" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F86" s="22" t="s">
+      <c r="F86" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G86" s="22" t="s">
+      <c r="G86" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H86" s="22" t="s">
+      <c r="H86" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I86" s="22" t="s">
+      <c r="I86" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J86" s="22" t="s">
+      <c r="J86" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K86" s="22" t="s">
+      <c r="K86" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L86" s="22" t="s">
+      <c r="L86" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M86" s="22" t="s">
+      <c r="M86" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N86" s="22" t="s">
+      <c r="N86" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O86" s="22" t="s">
+      <c r="O86" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P86" s="22" t="s">
+      <c r="P86" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:16">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D87" s="24" t="s">
+      <c r="D87" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E87" s="13" t="s">
+      <c r="E87" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F87" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G87" s="23" t="s">
+      <c r="G87" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H87" s="23" t="s">
+      <c r="H87" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="I87" s="23" t="s">
+      <c r="I87" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="J87" s="23" t="s">
+      <c r="J87" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="K87" s="27" t="s">
+      <c r="K87" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="L87" s="23" t="s">
+      <c r="L87" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M87" s="23" t="s">
+      <c r="M87" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="N87" s="23" t="s">
+      <c r="N87" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O87" s="23" t="s">
+      <c r="O87" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P87" s="23" t="s">
+      <c r="P87" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:16">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C88" s="16" t="s">
+      <c r="C88" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D88" s="24" t="s">
+      <c r="D88" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E88" s="13" t="s">
+      <c r="E88" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F88" s="13" t="s">
+      <c r="F88" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G88" s="23" t="s">
+      <c r="G88" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H88" s="23" t="s">
+      <c r="H88" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="I88" s="23" t="s">
+      <c r="I88" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J88" s="23" t="s">
+      <c r="J88" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="K88" s="27" t="s">
+      <c r="K88" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="L88" s="23" t="s">
+      <c r="L88" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="M88" s="23" t="s">
+      <c r="M88" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="N88" s="23" t="s">
+      <c r="N88" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="O88" s="23" t="s">
+      <c r="O88" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="P88" s="23" t="s">
+      <c r="P88" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:16">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D89" s="24" t="s">
+      <c r="D89" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E89" s="13" t="s">
+      <c r="E89" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F89" s="13" t="s">
+      <c r="F89" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G89" s="23" t="s">
+      <c r="G89" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="H89" s="23" t="s">
+      <c r="H89" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="I89" s="23" t="s">
+      <c r="I89" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="J89" s="23" t="s">
+      <c r="J89" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="K89" s="27" t="s">
+      <c r="K89" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="L89" s="23" t="s">
+      <c r="L89" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="M89" s="23" t="s">
+      <c r="M89" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="N89" s="23" t="s">
+      <c r="N89" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="O89" s="23" t="s">
+      <c r="O89" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="P89" s="23" t="s">
+      <c r="P89" s="22" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C90" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D90" s="24" t="s">
+      <c r="D90" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E90" s="13" t="s">
+      <c r="E90" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F90" s="13" t="s">
+      <c r="F90" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G90" s="23" t="s">
+      <c r="G90" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H90" s="23" t="s">
+      <c r="H90" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="I90" s="23" t="s">
+      <c r="I90" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="J90" s="23" t="s">
+      <c r="J90" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="K90" s="27" t="s">
+      <c r="K90" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="L90" s="23" t="s">
+      <c r="L90" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="M90" s="23" t="s">
+      <c r="M90" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="N90" s="23" t="s">
+      <c r="N90" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="O90" s="23" t="s">
+      <c r="O90" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="P90" s="23" t="s">
+      <c r="P90" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
+      <c r="A92" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B93" s="22" t="s">
+      <c r="B93" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="22" t="s">
+      <c r="C93" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D93" s="22" t="s">
+      <c r="D93" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E93" s="22" t="s">
+      <c r="E93" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F93" s="22" t="s">
+      <c r="F93" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G93" s="22" t="s">
+      <c r="G93" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H93" s="22" t="s">
+      <c r="H93" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I93" s="22" t="s">
+      <c r="I93" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J93" s="22" t="s">
+      <c r="J93" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K93" s="22" t="s">
+      <c r="K93" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L93" s="22" t="s">
+      <c r="L93" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M93" s="22" t="s">
+      <c r="M93" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N93" s="22" t="s">
+      <c r="N93" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" s="27" t="s">
+      <c r="A94" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B94" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="13" t="s">
+      <c r="E94" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F94" s="23" t="s">
+      <c r="F94" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G94" s="23" t="s">
+      <c r="G94" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H94" s="23" t="s">
+      <c r="H94" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I94" s="23" t="s">
+      <c r="I94" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="J94" s="27" t="s">
+      <c r="J94" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="K94" s="23" t="s">
+      <c r="K94" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="23" t="s">
+      <c r="L94" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="M94" s="23" t="s">
+      <c r="M94" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N94" s="23" t="s">
+      <c r="N94" s="22" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3799,43 +3710,43 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="10.5"/>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="10.199999999999999"/>
   <cols>
-    <col min="1" max="1" width="57.85546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="65" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="113" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="36.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="38.28515625" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" style="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="34.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="1" width="57.875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="65" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="113" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="36.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="38.25" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.375" style="19" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.75" style="19" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="34.125" style="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="29.25">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:17" ht="29.4">
+      <c r="A1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-    </row>
-    <row r="2" spans="1:18" s="21" customFormat="1">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+    </row>
+    <row r="2" spans="1:17" s="20" customFormat="1">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -3847,7 +3758,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:18" s="21" customFormat="1">
+    <row r="3" spans="1:17" s="20" customFormat="1">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -3873,7 +3784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" ht="21">
+    <row r="4" spans="1:17" s="10" customFormat="1" ht="20.399999999999999">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -3883,7 +3794,7 @@
       <c r="C4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -3895,437 +3806,424 @@
       <c r="G4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="29.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:17" ht="29.4">
+      <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="15" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="15" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="14" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="22" t="s">
+      <c r="J9" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="22" t="s">
+      <c r="K9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="22" t="s">
+      <c r="L9" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="22" t="s">
+      <c r="M9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="22" t="s">
+      <c r="N9" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="22" t="s">
+      <c r="O9" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="22" t="s">
+      <c r="P9" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="22" t="s">
+      <c r="Q9" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:17">
+      <c r="A10" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="27" t="s">
+      <c r="K10" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N10" s="23" t="s">
+      <c r="N10" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O10" s="23" t="s">
+      <c r="O10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P10" s="23" t="s">
+      <c r="P10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="Q10" s="23" t="s">
+      <c r="Q10" s="22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="15" t="s">
+    <row r="12" spans="1:17">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="22" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L14" s="22" t="s">
+      <c r="L14" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="22" t="s">
+      <c r="N14" s="21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="27" t="s">
+    <row r="15" spans="1:17">
+      <c r="A15" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-    </row>
-    <row r="17" spans="1:16" s="25" customFormat="1" ht="29.25">
-      <c r="A17" s="28" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+    </row>
+    <row r="17" spans="1:16" ht="29.4">
+      <c r="A17" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="12"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="22" t="s">
+      <c r="I20" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="22" t="s">
+      <c r="J20" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K20" s="22" t="s">
+      <c r="K20" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="22" t="s">
+      <c r="L20" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="M20" s="22" t="s">
+      <c r="M20" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N20" s="22" t="s">
+      <c r="N20" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="22" t="s">
+      <c r="O20" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="22" t="s">
+      <c r="P20" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J21" s="23" t="s">
+      <c r="J21" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="27" t="s">
+      <c r="K21" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L21" s="23" t="s">
+      <c r="L21" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M21" s="23" t="s">
+      <c r="M21" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N21" s="23" t="s">
+      <c r="N21" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="O21" s="23" t="s">
+      <c r="O21" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P21" s="23" t="s">
+      <c r="P21" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="J24" s="22" t="s">
+      <c r="J24" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="K24" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L24" s="22" t="s">
+      <c r="L24" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M24" s="22" t="s">
+      <c r="M24" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="N24" s="22" t="s">
+      <c r="N24" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
